--- a/artfynd/A 45841-2025 artfynd.xlsx
+++ b/artfynd/A 45841-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129342113</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45841-2025 artfynd.xlsx
+++ b/artfynd/A 45841-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129342113</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45841-2025 artfynd.xlsx
+++ b/artfynd/A 45841-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129342113</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45841-2025 artfynd.xlsx
+++ b/artfynd/A 45841-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129342113</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45841-2025 artfynd.xlsx
+++ b/artfynd/A 45841-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129342113</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45841-2025 artfynd.xlsx
+++ b/artfynd/A 45841-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129342113</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45841-2025 artfynd.xlsx
+++ b/artfynd/A 45841-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129342113</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45841-2025 artfynd.xlsx
+++ b/artfynd/A 45841-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129342113</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45841-2025 artfynd.xlsx
+++ b/artfynd/A 45841-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129341942</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129342113</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129342266</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45841-2025 artfynd.xlsx
+++ b/artfynd/A 45841-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129341942</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129342113</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129342266</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45841-2025 artfynd.xlsx
+++ b/artfynd/A 45841-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129341942</v>
+        <v>129342113</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598883</v>
+        <v>598909</v>
       </c>
       <c r="R2" t="n">
-        <v>6938199</v>
+        <v>6938311</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129342113</v>
+        <v>129341942</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598909</v>
+        <v>598883</v>
       </c>
       <c r="R3" t="n">
-        <v>6938311</v>
+        <v>6938199</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,6 +852,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +886,7 @@
         <v>129342266</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45841-2025 artfynd.xlsx
+++ b/artfynd/A 45841-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129342113</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45841-2025 artfynd.xlsx
+++ b/artfynd/A 45841-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>129341942</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129342266</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45841-2025 artfynd.xlsx
+++ b/artfynd/A 45841-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129342113</v>
+        <v>129341942</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598909</v>
+        <v>598883</v>
       </c>
       <c r="R2" t="n">
-        <v>6938311</v>
+        <v>6938199</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129341942</v>
+        <v>129342266</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598883</v>
+        <v>599017</v>
       </c>
       <c r="R3" t="n">
-        <v>6938199</v>
+        <v>6938476</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,38 +889,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129342266</v>
+        <v>129342113</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -923,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599017</v>
+        <v>598909</v>
       </c>
       <c r="R4" t="n">
-        <v>6938476</v>
+        <v>6938311</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,11 +964,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 45841-2025 artfynd.xlsx
+++ b/artfynd/A 45841-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129341942</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129342266</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,8 +1002,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129342113</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>